--- a/블로그/내가 한 게임들.xlsx
+++ b/블로그/내가 한 게임들.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\Desktop\unity_study\Game-Design\블로그\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42AA85B2-807B-4B57-8F20-C6081807D592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DAECF4-C796-44F9-BDF6-F08E6E07595D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{5EEC91C7-E8F3-4317-8F10-EA3E9515A5B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t>게임</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -184,6 +184,10 @@
   </si>
   <si>
     <t>https://maedyoung.tistory.com/9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://maedyoung.tistory.com/10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -648,6 +652,9 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
+      <c r="D4" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -761,19 +768,14 @@
     <hyperlink ref="D3" r:id="rId2" xr:uid="{9BB85407-0345-4A4C-83DB-1A3077D052B2}"/>
     <hyperlink ref="D7" r:id="rId3" xr:uid="{A192BF56-FB9F-4658-8B1A-BAD6C7F777D3}"/>
     <hyperlink ref="D9" r:id="rId4" xr:uid="{57A88409-03DF-4A95-A4C5-DDD9296173C8}"/>
+    <hyperlink ref="D4" r:id="rId5" xr:uid="{01E5BEFC-8DB2-4AD7-8ACC-344C877AAC1A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x0101004DEE7BE0B8FF844495DE62C43A369DA5" ma:contentTypeVersion="5" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="251ee00493409648c7fa179dce09d529">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="04230aae-5404-43e4-87ef-c28f577bb1f7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6be458cad489bea90c1b3d1311558deb" ns3:_="">
     <xsd:import namespace="04230aae-5404-43e4-87ef-c28f577bb1f7"/>
@@ -923,6 +925,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -933,22 +941,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D052613-9586-4474-9115-1D30632E499D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="04230aae-5404-43e4-87ef-c28f577bb1f7"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2ADFC980-CA99-4AF0-BED9-A89E01226A3F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -966,6 +958,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D052613-9586-4474-9115-1D30632E499D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="04230aae-5404-43e4-87ef-c28f577bb1f7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05976B79-33F9-44B8-AB4C-1DFA7A110AF4}">
   <ds:schemaRefs>
